--- a/course_evaluation_forms/007_e_learning_course_effectiveness_assessment_form--course_evaluation_forms.xlsx
+++ b/course_evaluation_forms/007_e_learning_course_effectiveness_assessment_form--course_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -803,17 +803,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>course_content_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>e-learning_is_not_effective</t>
+          <t>engaging_and_interactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E-learning is not effective</t>
+          <t>Engaging and interactive</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>engaging_and_interactive</t>
+          <t>relevant_and_up-to-date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engaging and interactive</t>
+          <t>Relevant and up-to-date</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>relevant_and_up-to-date</t>
+          <t>well-organized</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Relevant and up-to-date</t>
+          <t>Well-organized</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>well-organized</t>
+          <t>not_engaging_at_all</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Well-organized</t>
+          <t>Not engaging at all</t>
         </is>
       </c>
     </row>
@@ -876,29 +876,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_engaging_at_all</t>
+          <t>not_well-organized</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Not engaging at all</t>
+          <t>Not well-organized</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>course_content_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_well-organized</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not well-organized</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,10 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>overall_experience_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
